--- a/output/yearly_population_iteration_83_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_83_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4913</v>
+        <v>6348</v>
       </c>
       <c r="C2" t="n">
-        <v>4423</v>
+        <v>7267</v>
       </c>
       <c r="D2" t="n">
-        <v>30084</v>
+        <v>23147</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3478</v>
+        <v>3445</v>
       </c>
       <c r="C3" t="n">
-        <v>4878</v>
+        <v>7337</v>
       </c>
       <c r="D3" t="n">
-        <v>13939</v>
+        <v>12774</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2847</v>
+        <v>2979</v>
       </c>
       <c r="C4" t="n">
-        <v>6695</v>
+        <v>5100</v>
       </c>
       <c r="D4" t="n">
-        <v>6008</v>
+        <v>7922</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1898</v>
+        <v>2050</v>
       </c>
       <c r="C5" t="n">
-        <v>5344</v>
+        <v>5051</v>
       </c>
       <c r="D5" t="n">
-        <v>2082</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1051</v>
+        <v>1135</v>
       </c>
       <c r="C6" t="n">
-        <v>2448</v>
+        <v>3623</v>
       </c>
       <c r="D6" t="n">
-        <v>977</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C7" t="n">
-        <v>1020</v>
+        <v>2022</v>
       </c>
       <c r="D7" t="n">
-        <v>634</v>
+        <v>673</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C8" t="n">
-        <v>485</v>
+        <v>938</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>269</v>
+        <v>396</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
         <v>161</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7888</v>
+        <v>7798</v>
       </c>
       <c r="C2" t="n">
-        <v>6351</v>
+        <v>9101</v>
       </c>
       <c r="D2" t="n">
-        <v>23974</v>
+        <v>30260</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3379</v>
+        <v>3792</v>
       </c>
       <c r="C3" t="n">
-        <v>4087</v>
+        <v>6453</v>
       </c>
       <c r="D3" t="n">
-        <v>15304</v>
+        <v>13263</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2681</v>
+        <v>2722</v>
       </c>
       <c r="C4" t="n">
-        <v>5648</v>
+        <v>5975</v>
       </c>
       <c r="D4" t="n">
-        <v>7195</v>
+        <v>8350</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2071</v>
+        <v>2164</v>
       </c>
       <c r="C5" t="n">
-        <v>5830</v>
+        <v>4968</v>
       </c>
       <c r="D5" t="n">
-        <v>2639</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1293</v>
+        <v>1390</v>
       </c>
       <c r="C6" t="n">
-        <v>3785</v>
+        <v>4170</v>
       </c>
       <c r="D6" t="n">
-        <v>1144</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>670</v>
+        <v>687</v>
       </c>
       <c r="C7" t="n">
-        <v>1667</v>
+        <v>2711</v>
       </c>
       <c r="D7" t="n">
-        <v>681</v>
+        <v>757</v>
       </c>
     </row>
     <row r="8">
@@ -1175,10 +1175,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C8" t="n">
-        <v>725</v>
+        <v>1374</v>
       </c>
       <c r="D8" t="n">
         <v>453</v>
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
-        <v>359</v>
+        <v>609</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8232</v>
+        <v>8058</v>
       </c>
       <c r="C2" t="n">
-        <v>8623</v>
+        <v>15106</v>
       </c>
       <c r="D2" t="n">
-        <v>22863</v>
+        <v>29285</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4251</v>
+        <v>4375</v>
       </c>
       <c r="C3" t="n">
-        <v>4479</v>
+        <v>6672</v>
       </c>
       <c r="D3" t="n">
-        <v>15409</v>
+        <v>14453</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2567</v>
+        <v>2670</v>
       </c>
       <c r="C4" t="n">
-        <v>4811</v>
+        <v>6052</v>
       </c>
       <c r="D4" t="n">
-        <v>8152</v>
+        <v>8803</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2073</v>
+        <v>2131</v>
       </c>
       <c r="C5" t="n">
-        <v>5572</v>
+        <v>5222</v>
       </c>
       <c r="D5" t="n">
-        <v>3258</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1472</v>
+        <v>1540</v>
       </c>
       <c r="C6" t="n">
-        <v>4632</v>
+        <v>4407</v>
       </c>
       <c r="D6" t="n">
-        <v>1332</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>832</v>
+        <v>855</v>
       </c>
       <c r="C7" t="n">
-        <v>2542</v>
+        <v>3255</v>
       </c>
       <c r="D7" t="n">
-        <v>742</v>
+        <v>856</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="C8" t="n">
-        <v>1112</v>
+        <v>1884</v>
       </c>
       <c r="D8" t="n">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C9" t="n">
-        <v>498</v>
+        <v>880</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>277</v>
+        <v>397</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7465</v>
+        <v>7461</v>
       </c>
       <c r="C2" t="n">
-        <v>5725</v>
+        <v>10513</v>
       </c>
       <c r="D2" t="n">
-        <v>18699</v>
+        <v>24121</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4939</v>
+        <v>4995</v>
       </c>
       <c r="C3" t="n">
-        <v>7366</v>
+        <v>10532</v>
       </c>
       <c r="D3" t="n">
-        <v>16809</v>
+        <v>15885</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1915</v>
+        <v>1969</v>
       </c>
       <c r="C4" t="n">
-        <v>8074</v>
+        <v>8266</v>
       </c>
       <c r="D4" t="n">
-        <v>7620</v>
+        <v>8715</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1360</v>
+        <v>1422</v>
       </c>
       <c r="C5" t="n">
-        <v>4539</v>
+        <v>4318</v>
       </c>
       <c r="D5" t="n">
-        <v>2212</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>768</v>
+        <v>790</v>
       </c>
       <c r="C6" t="n">
-        <v>2491</v>
+        <v>3189</v>
       </c>
       <c r="D6" t="n">
-        <v>727</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>1089</v>
+        <v>1846</v>
       </c>
       <c r="D7" t="n">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>488</v>
+        <v>862</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>271</v>
+        <v>389</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4509</v>
+        <v>4562</v>
       </c>
       <c r="C2" t="n">
-        <v>2735</v>
+        <v>4853</v>
       </c>
       <c r="D2" t="n">
-        <v>14382</v>
+        <v>16914</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5201</v>
+        <v>5179</v>
       </c>
       <c r="C3" t="n">
-        <v>5963</v>
+        <v>9563</v>
       </c>
       <c r="D3" t="n">
-        <v>16247</v>
+        <v>16242</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2705</v>
+        <v>2679</v>
       </c>
       <c r="C4" t="n">
-        <v>7798</v>
+        <v>9354</v>
       </c>
       <c r="D4" t="n">
-        <v>8872</v>
+        <v>9566</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1508</v>
+        <v>1558</v>
       </c>
       <c r="C5" t="n">
-        <v>6189</v>
+        <v>6027</v>
       </c>
       <c r="D5" t="n">
-        <v>2935</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="C6" t="n">
-        <v>3389</v>
+        <v>3763</v>
       </c>
       <c r="D6" t="n">
-        <v>882</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="C7" t="n">
-        <v>1572</v>
+        <v>2332</v>
       </c>
       <c r="D7" t="n">
-        <v>503</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>673</v>
+        <v>1151</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>325</v>
+        <v>424</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4594</v>
+        <v>4731</v>
       </c>
       <c r="C2" t="n">
-        <v>3276</v>
+        <v>5162</v>
       </c>
       <c r="D2" t="n">
-        <v>14346</v>
+        <v>13384</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4112</v>
+        <v>4180</v>
       </c>
       <c r="C3" t="n">
-        <v>3872</v>
+        <v>6531</v>
       </c>
       <c r="D3" t="n">
-        <v>14860</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3288</v>
+        <v>3180</v>
       </c>
       <c r="C4" t="n">
-        <v>6702</v>
+        <v>9259</v>
       </c>
       <c r="D4" t="n">
-        <v>9876</v>
+        <v>10364</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1799</v>
+        <v>1803</v>
       </c>
       <c r="C5" t="n">
-        <v>6907</v>
+        <v>7492</v>
       </c>
       <c r="D5" t="n">
-        <v>3814</v>
+        <v>4446</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1083</v>
+        <v>1094</v>
       </c>
       <c r="C6" t="n">
-        <v>4645</v>
+        <v>4705</v>
       </c>
       <c r="D6" t="n">
-        <v>1185</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>516</v>
+        <v>484</v>
       </c>
       <c r="C7" t="n">
-        <v>2405</v>
+        <v>2956</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="C8" t="n">
-        <v>1058</v>
+        <v>1624</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>464</v>
+        <v>691</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>102</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2679</v>
+        <v>2850</v>
       </c>
       <c r="C2" t="n">
-        <v>1502</v>
+        <v>2468</v>
       </c>
       <c r="D2" t="n">
-        <v>9906</v>
+        <v>9344</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4117</v>
+        <v>4193</v>
       </c>
       <c r="C3" t="n">
-        <v>3532</v>
+        <v>5893</v>
       </c>
       <c r="D3" t="n">
-        <v>14445</v>
+        <v>14706</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3642</v>
+        <v>3486</v>
       </c>
       <c r="C4" t="n">
-        <v>6227</v>
+        <v>9091</v>
       </c>
       <c r="D4" t="n">
-        <v>10528</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1886</v>
+        <v>1892</v>
       </c>
       <c r="C5" t="n">
-        <v>7892</v>
+        <v>9094</v>
       </c>
       <c r="D5" t="n">
-        <v>4156</v>
+        <v>4674</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>937</v>
+        <v>881</v>
       </c>
       <c r="C6" t="n">
-        <v>5564</v>
+        <v>5560</v>
       </c>
       <c r="D6" t="n">
-        <v>1175</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>2320</v>
+        <v>3026</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>796</v>
+        <v>1154</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3734</v>
+        <v>3426</v>
       </c>
       <c r="C2" t="n">
-        <v>5443</v>
+        <v>4650</v>
       </c>
       <c r="D2" t="n">
-        <v>10445</v>
+        <v>10626</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2991</v>
+        <v>3126</v>
       </c>
       <c r="C3" t="n">
-        <v>2286</v>
+        <v>3909</v>
       </c>
       <c r="D3" t="n">
-        <v>12936</v>
+        <v>13129</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3393</v>
+        <v>3288</v>
       </c>
       <c r="C4" t="n">
-        <v>4778</v>
+        <v>7515</v>
       </c>
       <c r="D4" t="n">
-        <v>10847</v>
+        <v>11243</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2315</v>
+        <v>2245</v>
       </c>
       <c r="C5" t="n">
-        <v>7020</v>
+        <v>8903</v>
       </c>
       <c r="D5" t="n">
-        <v>5008</v>
+        <v>5444</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1198</v>
+        <v>1144</v>
       </c>
       <c r="C6" t="n">
-        <v>6647</v>
+        <v>7077</v>
       </c>
       <c r="D6" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="C7" t="n">
-        <v>3677</v>
+        <v>4022</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1401</v>
+        <v>1836</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>442</v>
+        <v>570</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2817</v>
+        <v>2319</v>
       </c>
       <c r="C2" t="n">
-        <v>3230</v>
+        <v>4169</v>
       </c>
       <c r="D2" t="n">
-        <v>7585</v>
+        <v>8943</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2838</v>
+        <v>2822</v>
       </c>
       <c r="C3" t="n">
-        <v>3275</v>
+        <v>3813</v>
       </c>
       <c r="D3" t="n">
-        <v>12016</v>
+        <v>12155</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3012</v>
+        <v>2985</v>
       </c>
       <c r="C4" t="n">
-        <v>3763</v>
+        <v>6155</v>
       </c>
       <c r="D4" t="n">
-        <v>10902</v>
+        <v>11244</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2533</v>
+        <v>2413</v>
       </c>
       <c r="C5" t="n">
-        <v>6236</v>
+        <v>8494</v>
       </c>
       <c r="D5" t="n">
-        <v>5624</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1407</v>
+        <v>1332</v>
       </c>
       <c r="C6" t="n">
-        <v>7046</v>
+        <v>7920</v>
       </c>
       <c r="D6" t="n">
-        <v>1906</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>348</v>
+        <v>286</v>
       </c>
       <c r="C7" t="n">
-        <v>4713</v>
+        <v>5014</v>
       </c>
       <c r="D7" t="n">
-        <v>712</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1952</v>
+        <v>2352</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>543</v>
+        <v>645</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4883</v>
+        <v>3230</v>
       </c>
       <c r="C2" t="n">
-        <v>4918</v>
+        <v>6612</v>
       </c>
       <c r="D2" t="n">
-        <v>12245</v>
+        <v>10263</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2379</v>
+        <v>2230</v>
       </c>
       <c r="C3" t="n">
-        <v>2912</v>
+        <v>3520</v>
       </c>
       <c r="D3" t="n">
-        <v>10660</v>
+        <v>11108</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2562</v>
+        <v>2545</v>
       </c>
       <c r="C4" t="n">
-        <v>3469</v>
+        <v>5060</v>
       </c>
       <c r="D4" t="n">
-        <v>10741</v>
+        <v>10916</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2466</v>
+        <v>2399</v>
       </c>
       <c r="C5" t="n">
-        <v>5061</v>
+        <v>7396</v>
       </c>
       <c r="D5" t="n">
-        <v>6213</v>
+        <v>6518</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1682</v>
+        <v>1567</v>
       </c>
       <c r="C6" t="n">
-        <v>6657</v>
+        <v>8069</v>
       </c>
       <c r="D6" t="n">
-        <v>2380</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>624</v>
+        <v>533</v>
       </c>
       <c r="C7" t="n">
-        <v>5625</v>
+        <v>6065</v>
       </c>
       <c r="D7" t="n">
-        <v>856</v>
+        <v>894</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>2998</v>
+        <v>3287</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1031</v>
+        <v>1186</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5262</v>
+        <v>6972</v>
       </c>
       <c r="C2" t="n">
-        <v>2568</v>
+        <v>9381</v>
       </c>
       <c r="D2" t="n">
-        <v>4868</v>
+        <v>17773</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3454</v>
+        <v>2337</v>
       </c>
       <c r="C2" t="n">
-        <v>2715</v>
+        <v>3862</v>
       </c>
       <c r="D2" t="n">
-        <v>9012</v>
+        <v>7635</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3281</v>
+        <v>3004</v>
       </c>
       <c r="C3" t="n">
-        <v>3651</v>
+        <v>4503</v>
       </c>
       <c r="D3" t="n">
-        <v>11635</v>
+        <v>11971</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3584</v>
+        <v>3495</v>
       </c>
       <c r="C4" t="n">
-        <v>5151</v>
+        <v>7575</v>
       </c>
       <c r="D4" t="n">
-        <v>11124</v>
+        <v>11310</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1645</v>
+        <v>1492</v>
       </c>
       <c r="C5" t="n">
-        <v>8489</v>
+        <v>11091</v>
       </c>
       <c r="D5" t="n">
-        <v>5699</v>
+        <v>5968</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>576</v>
+        <v>492</v>
       </c>
       <c r="C6" t="n">
-        <v>6947</v>
+        <v>7446</v>
       </c>
       <c r="D6" t="n">
-        <v>1887</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>2938</v>
+        <v>3221</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1010</v>
+        <v>1162</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6844</v>
+        <v>6943</v>
       </c>
       <c r="C2" t="n">
-        <v>3033</v>
+        <v>4747</v>
       </c>
       <c r="D2" t="n">
-        <v>6611</v>
+        <v>17608</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2236</v>
+        <v>2961</v>
       </c>
       <c r="C3" t="n">
-        <v>1314</v>
+        <v>4728</v>
       </c>
       <c r="D3" t="n">
-        <v>1488</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="4">
@@ -4543,10 +4543,10 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
-        <v>1546</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="5">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4555</v>
+        <v>5078</v>
       </c>
       <c r="C2" t="n">
-        <v>3664</v>
+        <v>8675</v>
       </c>
       <c r="D2" t="n">
-        <v>12697</v>
+        <v>28272</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3761</v>
+        <v>4068</v>
       </c>
       <c r="C3" t="n">
-        <v>1983</v>
+        <v>4086</v>
       </c>
       <c r="D3" t="n">
-        <v>2239</v>
+        <v>5707</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1024</v>
+        <v>1320</v>
       </c>
       <c r="C4" t="n">
-        <v>825</v>
+        <v>2814</v>
       </c>
       <c r="D4" t="n">
-        <v>1487</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1188</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4924,10 +4924,10 @@
         <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12">
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4678</v>
+        <v>6465</v>
       </c>
       <c r="C2" t="n">
-        <v>5373</v>
+        <v>8642</v>
       </c>
       <c r="D2" t="n">
-        <v>13664</v>
+        <v>29895</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3424</v>
+        <v>3792</v>
       </c>
       <c r="C3" t="n">
-        <v>2520</v>
+        <v>5672</v>
       </c>
       <c r="D3" t="n">
-        <v>3751</v>
+        <v>8906</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2055</v>
+        <v>2259</v>
       </c>
       <c r="C4" t="n">
-        <v>1474</v>
+        <v>3463</v>
       </c>
       <c r="D4" t="n">
-        <v>1571</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>479</v>
+        <v>592</v>
       </c>
       <c r="C5" t="n">
-        <v>552</v>
+        <v>1610</v>
       </c>
       <c r="D5" t="n">
-        <v>1209</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D6" t="n">
-        <v>911</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5816</v>
+        <v>7293</v>
       </c>
       <c r="C2" t="n">
-        <v>11648</v>
+        <v>9557</v>
       </c>
       <c r="D2" t="n">
-        <v>23082</v>
+        <v>29292</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3313</v>
+        <v>4123</v>
       </c>
       <c r="C3" t="n">
-        <v>3509</v>
+        <v>6252</v>
       </c>
       <c r="D3" t="n">
-        <v>5067</v>
+        <v>11469</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2328</v>
+        <v>2563</v>
       </c>
       <c r="C4" t="n">
-        <v>2025</v>
+        <v>4557</v>
       </c>
       <c r="D4" t="n">
-        <v>1941</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1066</v>
+        <v>1158</v>
       </c>
       <c r="C5" t="n">
-        <v>1036</v>
+        <v>2503</v>
       </c>
       <c r="D5" t="n">
-        <v>1238</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="C6" t="n">
-        <v>423</v>
+        <v>953</v>
       </c>
       <c r="D6" t="n">
-        <v>940</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6745</v>
+        <v>6530</v>
       </c>
       <c r="C2" t="n">
-        <v>12883</v>
+        <v>7967</v>
       </c>
       <c r="D2" t="n">
-        <v>31764</v>
+        <v>23863</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3331</v>
+        <v>4080</v>
       </c>
       <c r="C3" t="n">
-        <v>6405</v>
+        <v>6483</v>
       </c>
       <c r="D3" t="n">
-        <v>7144</v>
+        <v>12579</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1773</v>
+        <v>2045</v>
       </c>
       <c r="C4" t="n">
-        <v>2358</v>
+        <v>4479</v>
       </c>
       <c r="D4" t="n">
-        <v>2167</v>
+        <v>4337</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>893</v>
+        <v>968</v>
       </c>
       <c r="C5" t="n">
-        <v>1141</v>
+        <v>2572</v>
       </c>
       <c r="D5" t="n">
-        <v>1067</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="C6" t="n">
-        <v>501</v>
+        <v>1157</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>248</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>273</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5117</v>
+        <v>5436</v>
       </c>
       <c r="C2" t="n">
-        <v>6899</v>
+        <v>4482</v>
       </c>
       <c r="D2" t="n">
-        <v>29299</v>
+        <v>18992</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4244</v>
+        <v>4385</v>
       </c>
       <c r="C3" t="n">
-        <v>8954</v>
+        <v>6316</v>
       </c>
       <c r="D3" t="n">
-        <v>10939</v>
+        <v>13548</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2270</v>
+        <v>2678</v>
       </c>
       <c r="C4" t="n">
-        <v>4811</v>
+        <v>5578</v>
       </c>
       <c r="D4" t="n">
-        <v>3152</v>
+        <v>5866</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1204</v>
+        <v>1336</v>
       </c>
       <c r="C5" t="n">
-        <v>1864</v>
+        <v>3616</v>
       </c>
       <c r="D5" t="n">
-        <v>1246</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="C6" t="n">
-        <v>875</v>
+        <v>1930</v>
       </c>
       <c r="D6" t="n">
-        <v>807</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C7" t="n">
-        <v>396</v>
+        <v>814</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>236</v>
+        <v>321</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4617</v>
+        <v>4327</v>
       </c>
       <c r="C2" t="n">
-        <v>4475</v>
+        <v>12355</v>
       </c>
       <c r="D2" t="n">
-        <v>24090</v>
+        <v>15341</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3859</v>
+        <v>4030</v>
       </c>
       <c r="C3" t="n">
-        <v>6719</v>
+        <v>4651</v>
       </c>
       <c r="D3" t="n">
-        <v>13218</v>
+        <v>13421</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2830</v>
+        <v>3025</v>
       </c>
       <c r="C4" t="n">
-        <v>7137</v>
+        <v>5812</v>
       </c>
       <c r="D4" t="n">
-        <v>4626</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1526</v>
+        <v>1728</v>
       </c>
       <c r="C5" t="n">
-        <v>3494</v>
+        <v>4595</v>
       </c>
       <c r="D5" t="n">
-        <v>1574</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>819</v>
+        <v>868</v>
       </c>
       <c r="C6" t="n">
-        <v>1397</v>
+        <v>2782</v>
       </c>
       <c r="D6" t="n">
-        <v>867</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>658</v>
+        <v>1374</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -6465,10 +6465,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>320</v>
+        <v>567</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>224</v>
+        <v>263</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_83_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_83_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6348</v>
+        <v>5876</v>
       </c>
       <c r="C2" t="n">
-        <v>7267</v>
+        <v>11840</v>
       </c>
       <c r="D2" t="n">
-        <v>23147</v>
+        <v>37670</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3445</v>
+        <v>4046</v>
       </c>
       <c r="C3" t="n">
-        <v>7337</v>
+        <v>6001</v>
       </c>
       <c r="D3" t="n">
-        <v>12774</v>
+        <v>16822</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2979</v>
+        <v>3504</v>
       </c>
       <c r="C4" t="n">
-        <v>5100</v>
+        <v>6742</v>
       </c>
       <c r="D4" t="n">
-        <v>7922</v>
+        <v>8017</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2050</v>
+        <v>2257</v>
       </c>
       <c r="C5" t="n">
-        <v>5051</v>
+        <v>4722</v>
       </c>
       <c r="D5" t="n">
-        <v>3220</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1135</v>
+        <v>1162</v>
       </c>
       <c r="C6" t="n">
-        <v>3623</v>
+        <v>2703</v>
       </c>
       <c r="D6" t="n">
-        <v>1294</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C7" t="n">
-        <v>2022</v>
+        <v>1482</v>
       </c>
       <c r="D7" t="n">
-        <v>673</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C8" t="n">
-        <v>938</v>
+        <v>644</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>396</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
         <v>161</v>
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7798</v>
+        <v>7197</v>
       </c>
       <c r="C2" t="n">
-        <v>9101</v>
+        <v>15976</v>
       </c>
       <c r="D2" t="n">
-        <v>30260</v>
+        <v>37809</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3792</v>
+        <v>3961</v>
       </c>
       <c r="C3" t="n">
-        <v>6453</v>
+        <v>7579</v>
       </c>
       <c r="D3" t="n">
-        <v>13263</v>
+        <v>18526</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2722</v>
+        <v>3204</v>
       </c>
       <c r="C4" t="n">
-        <v>5975</v>
+        <v>6188</v>
       </c>
       <c r="D4" t="n">
-        <v>8350</v>
+        <v>9210</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2164</v>
+        <v>2487</v>
       </c>
       <c r="C5" t="n">
-        <v>4968</v>
+        <v>5554</v>
       </c>
       <c r="D5" t="n">
-        <v>3844</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1390</v>
+        <v>1468</v>
       </c>
       <c r="C6" t="n">
-        <v>4170</v>
+        <v>3542</v>
       </c>
       <c r="D6" t="n">
-        <v>1541</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>687</v>
+        <v>705</v>
       </c>
       <c r="C7" t="n">
-        <v>2711</v>
+        <v>2019</v>
       </c>
       <c r="D7" t="n">
-        <v>757</v>
+        <v>726</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C8" t="n">
-        <v>1374</v>
+        <v>990</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
-        <v>609</v>
+        <v>436</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8058</v>
+        <v>10154</v>
       </c>
       <c r="C2" t="n">
-        <v>15106</v>
+        <v>16723</v>
       </c>
       <c r="D2" t="n">
-        <v>29285</v>
+        <v>43899</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4375</v>
+        <v>4256</v>
       </c>
       <c r="C3" t="n">
-        <v>6672</v>
+        <v>9698</v>
       </c>
       <c r="D3" t="n">
-        <v>14453</v>
+        <v>19654</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2670</v>
+        <v>2995</v>
       </c>
       <c r="C4" t="n">
-        <v>6052</v>
+        <v>6587</v>
       </c>
       <c r="D4" t="n">
-        <v>8803</v>
+        <v>10183</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2131</v>
+        <v>2476</v>
       </c>
       <c r="C5" t="n">
-        <v>5222</v>
+        <v>5646</v>
       </c>
       <c r="D5" t="n">
-        <v>4295</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1540</v>
+        <v>1713</v>
       </c>
       <c r="C6" t="n">
-        <v>4407</v>
+        <v>4322</v>
       </c>
       <c r="D6" t="n">
-        <v>1815</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>855</v>
+        <v>890</v>
       </c>
       <c r="C7" t="n">
-        <v>3255</v>
+        <v>2595</v>
       </c>
       <c r="D7" t="n">
-        <v>856</v>
+        <v>815</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="C8" t="n">
-        <v>1884</v>
+        <v>1373</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C9" t="n">
-        <v>880</v>
+        <v>642</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>397</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7461</v>
+        <v>9112</v>
       </c>
       <c r="C2" t="n">
-        <v>10513</v>
+        <v>11639</v>
       </c>
       <c r="D2" t="n">
-        <v>24121</v>
+        <v>36062</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4995</v>
+        <v>5198</v>
       </c>
       <c r="C3" t="n">
-        <v>10532</v>
+        <v>13831</v>
       </c>
       <c r="D3" t="n">
-        <v>15885</v>
+        <v>21052</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1969</v>
+        <v>2287</v>
       </c>
       <c r="C4" t="n">
-        <v>8266</v>
+        <v>8961</v>
       </c>
       <c r="D4" t="n">
-        <v>8715</v>
+        <v>9614</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1422</v>
+        <v>1582</v>
       </c>
       <c r="C5" t="n">
-        <v>4318</v>
+        <v>4235</v>
       </c>
       <c r="D5" t="n">
-        <v>2933</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>790</v>
+        <v>822</v>
       </c>
       <c r="C6" t="n">
-        <v>3189</v>
+        <v>2543</v>
       </c>
       <c r="D6" t="n">
-        <v>838</v>
+        <v>798</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="C7" t="n">
-        <v>1846</v>
+        <v>1345</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C8" t="n">
-        <v>862</v>
+        <v>629</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>389</v>
+        <v>297</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4562</v>
+        <v>5421</v>
       </c>
       <c r="C2" t="n">
-        <v>4853</v>
+        <v>5019</v>
       </c>
       <c r="D2" t="n">
-        <v>16914</v>
+        <v>24797</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5179</v>
+        <v>5810</v>
       </c>
       <c r="C3" t="n">
-        <v>9563</v>
+        <v>11692</v>
       </c>
       <c r="D3" t="n">
-        <v>16242</v>
+        <v>22082</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2679</v>
+        <v>2942</v>
       </c>
       <c r="C4" t="n">
-        <v>9354</v>
+        <v>11230</v>
       </c>
       <c r="D4" t="n">
-        <v>9566</v>
+        <v>11061</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1558</v>
+        <v>1754</v>
       </c>
       <c r="C5" t="n">
-        <v>6027</v>
+        <v>6255</v>
       </c>
       <c r="D5" t="n">
-        <v>3649</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>926</v>
+        <v>975</v>
       </c>
       <c r="C6" t="n">
-        <v>3763</v>
+        <v>3267</v>
       </c>
       <c r="D6" t="n">
-        <v>1033</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C7" t="n">
-        <v>2332</v>
+        <v>1755</v>
       </c>
       <c r="D7" t="n">
         <v>516</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>1151</v>
+        <v>838</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>424</v>
+        <v>334</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4731</v>
+        <v>6100</v>
       </c>
       <c r="C2" t="n">
-        <v>5162</v>
+        <v>3633</v>
       </c>
       <c r="D2" t="n">
-        <v>13384</v>
+        <v>22784</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4180</v>
+        <v>4748</v>
       </c>
       <c r="C3" t="n">
-        <v>6531</v>
+        <v>7732</v>
       </c>
       <c r="D3" t="n">
-        <v>15241</v>
+        <v>20967</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3180</v>
+        <v>3559</v>
       </c>
       <c r="C4" t="n">
-        <v>9259</v>
+        <v>11213</v>
       </c>
       <c r="D4" t="n">
-        <v>10364</v>
+        <v>12523</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1803</v>
+        <v>1997</v>
       </c>
       <c r="C5" t="n">
-        <v>7492</v>
+        <v>8369</v>
       </c>
       <c r="D5" t="n">
-        <v>4446</v>
+        <v>4679</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1094</v>
+        <v>1172</v>
       </c>
       <c r="C6" t="n">
-        <v>4705</v>
+        <v>4527</v>
       </c>
       <c r="D6" t="n">
-        <v>1396</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="C7" t="n">
-        <v>2956</v>
+        <v>2408</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C8" t="n">
-        <v>1624</v>
+        <v>1205</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2436,7 +2436,7 @@
         <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>691</v>
+        <v>519</v>
       </c>
       <c r="D9" t="n">
         <v>264</v>
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2481,7 +2481,7 @@
         <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2850</v>
+        <v>3705</v>
       </c>
       <c r="C2" t="n">
-        <v>2468</v>
+        <v>1760</v>
       </c>
       <c r="D2" t="n">
-        <v>9344</v>
+        <v>15892</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4193</v>
+        <v>4877</v>
       </c>
       <c r="C3" t="n">
-        <v>5893</v>
+        <v>6210</v>
       </c>
       <c r="D3" t="n">
-        <v>14706</v>
+        <v>20686</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3486</v>
+        <v>3923</v>
       </c>
       <c r="C4" t="n">
-        <v>9091</v>
+        <v>10986</v>
       </c>
       <c r="D4" t="n">
-        <v>11010</v>
+        <v>13562</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1892</v>
+        <v>2067</v>
       </c>
       <c r="C5" t="n">
-        <v>9094</v>
+        <v>10176</v>
       </c>
       <c r="D5" t="n">
-        <v>4674</v>
+        <v>4922</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>881</v>
+        <v>919</v>
       </c>
       <c r="C6" t="n">
-        <v>5560</v>
+        <v>5249</v>
       </c>
       <c r="D6" t="n">
-        <v>1359</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C7" t="n">
-        <v>3026</v>
+        <v>2395</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1154</v>
+        <v>851</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2778,7 +2778,7 @@
         <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3426</v>
+        <v>5122</v>
       </c>
       <c r="C2" t="n">
-        <v>4650</v>
+        <v>8084</v>
       </c>
       <c r="D2" t="n">
-        <v>10626</v>
+        <v>16877</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3126</v>
+        <v>3773</v>
       </c>
       <c r="C3" t="n">
-        <v>3909</v>
+        <v>3835</v>
       </c>
       <c r="D3" t="n">
-        <v>13129</v>
+        <v>18715</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3288</v>
+        <v>3743</v>
       </c>
       <c r="C4" t="n">
-        <v>7515</v>
+        <v>8708</v>
       </c>
       <c r="D4" t="n">
-        <v>11243</v>
+        <v>14243</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2245</v>
+        <v>2473</v>
       </c>
       <c r="C5" t="n">
-        <v>8903</v>
+        <v>10306</v>
       </c>
       <c r="D5" t="n">
-        <v>5444</v>
+        <v>6063</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1144</v>
+        <v>1209</v>
       </c>
       <c r="C6" t="n">
-        <v>7077</v>
+        <v>7292</v>
       </c>
       <c r="D6" t="n">
-        <v>1800</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>4022</v>
+        <v>3480</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1836</v>
+        <v>1396</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>570</v>
+        <v>441</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3173,7 +3173,7 @@
         <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2319</v>
+        <v>3474</v>
       </c>
       <c r="C2" t="n">
-        <v>4169</v>
+        <v>4276</v>
       </c>
       <c r="D2" t="n">
-        <v>8943</v>
+        <v>12700</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2822</v>
+        <v>3666</v>
       </c>
       <c r="C3" t="n">
-        <v>3813</v>
+        <v>4925</v>
       </c>
       <c r="D3" t="n">
-        <v>12155</v>
+        <v>17520</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2985</v>
+        <v>3451</v>
       </c>
       <c r="C4" t="n">
-        <v>6155</v>
+        <v>6906</v>
       </c>
       <c r="D4" t="n">
-        <v>11244</v>
+        <v>14504</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2413</v>
+        <v>2671</v>
       </c>
       <c r="C5" t="n">
-        <v>8494</v>
+        <v>9950</v>
       </c>
       <c r="D5" t="n">
-        <v>5995</v>
+        <v>6858</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1332</v>
+        <v>1398</v>
       </c>
       <c r="C6" t="n">
-        <v>7920</v>
+        <v>8443</v>
       </c>
       <c r="D6" t="n">
-        <v>2093</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C7" t="n">
-        <v>5014</v>
+        <v>4505</v>
       </c>
       <c r="D7" t="n">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2352</v>
+        <v>1848</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>645</v>
+        <v>476</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
         <v>91</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" t="n">
         <v>35</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3470,7 +3470,7 @@
         <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3230</v>
+        <v>5029</v>
       </c>
       <c r="C2" t="n">
-        <v>6612</v>
+        <v>8861</v>
       </c>
       <c r="D2" t="n">
-        <v>10263</v>
+        <v>19091</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2230</v>
+        <v>3037</v>
       </c>
       <c r="C3" t="n">
-        <v>3520</v>
+        <v>4226</v>
       </c>
       <c r="D3" t="n">
-        <v>11108</v>
+        <v>15886</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2545</v>
+        <v>3059</v>
       </c>
       <c r="C4" t="n">
-        <v>5060</v>
+        <v>5982</v>
       </c>
       <c r="D4" t="n">
-        <v>10916</v>
+        <v>14468</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2399</v>
+        <v>2663</v>
       </c>
       <c r="C5" t="n">
-        <v>7396</v>
+        <v>8507</v>
       </c>
       <c r="D5" t="n">
-        <v>6518</v>
+        <v>7603</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1567</v>
+        <v>1671</v>
       </c>
       <c r="C6" t="n">
-        <v>8069</v>
+        <v>8925</v>
       </c>
       <c r="D6" t="n">
-        <v>2553</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="C7" t="n">
-        <v>6065</v>
+        <v>5936</v>
       </c>
       <c r="D7" t="n">
-        <v>894</v>
+        <v>891</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>3287</v>
+        <v>2706</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1186</v>
+        <v>897</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>343</v>
+        <v>283</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6972</v>
+        <v>6093</v>
       </c>
       <c r="C2" t="n">
-        <v>9381</v>
+        <v>3034</v>
       </c>
       <c r="D2" t="n">
-        <v>17773</v>
+        <v>11625</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2337</v>
+        <v>3715</v>
       </c>
       <c r="C2" t="n">
-        <v>3862</v>
+        <v>5245</v>
       </c>
       <c r="D2" t="n">
-        <v>7635</v>
+        <v>14203</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3004</v>
+        <v>3951</v>
       </c>
       <c r="C3" t="n">
-        <v>4503</v>
+        <v>5690</v>
       </c>
       <c r="D3" t="n">
-        <v>11971</v>
+        <v>17430</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3495</v>
+        <v>4024</v>
       </c>
       <c r="C4" t="n">
-        <v>7575</v>
+        <v>8810</v>
       </c>
       <c r="D4" t="n">
-        <v>11310</v>
+        <v>14675</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1492</v>
+        <v>1544</v>
       </c>
       <c r="C5" t="n">
-        <v>11091</v>
+        <v>12567</v>
       </c>
       <c r="D5" t="n">
-        <v>5968</v>
+        <v>6696</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C6" t="n">
-        <v>7446</v>
+        <v>7304</v>
       </c>
       <c r="D6" t="n">
-        <v>1988</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>3221</v>
+        <v>2651</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>534</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1162</v>
+        <v>879</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6943</v>
+        <v>6907</v>
       </c>
       <c r="C2" t="n">
-        <v>4747</v>
+        <v>6182</v>
       </c>
       <c r="D2" t="n">
-        <v>17608</v>
+        <v>12803</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2961</v>
+        <v>2589</v>
       </c>
       <c r="C3" t="n">
-        <v>4728</v>
+        <v>1529</v>
       </c>
       <c r="D3" t="n">
-        <v>3625</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5078</v>
+        <v>5069</v>
       </c>
       <c r="C2" t="n">
-        <v>8675</v>
+        <v>6731</v>
       </c>
       <c r="D2" t="n">
-        <v>28272</v>
+        <v>23124</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4068</v>
+        <v>3898</v>
       </c>
       <c r="C3" t="n">
-        <v>4086</v>
+        <v>3624</v>
       </c>
       <c r="D3" t="n">
-        <v>5707</v>
+        <v>4116</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1320</v>
+        <v>1158</v>
       </c>
       <c r="C4" t="n">
-        <v>2814</v>
+        <v>953</v>
       </c>
       <c r="D4" t="n">
-        <v>1911</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6465</v>
+        <v>6985</v>
       </c>
       <c r="C2" t="n">
-        <v>8642</v>
+        <v>6033</v>
       </c>
       <c r="D2" t="n">
-        <v>29895</v>
+        <v>30715</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3792</v>
+        <v>3680</v>
       </c>
       <c r="C3" t="n">
-        <v>5672</v>
+        <v>4603</v>
       </c>
       <c r="D3" t="n">
-        <v>8906</v>
+        <v>6860</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2259</v>
+        <v>2140</v>
       </c>
       <c r="C4" t="n">
-        <v>3463</v>
+        <v>2446</v>
       </c>
       <c r="D4" t="n">
-        <v>2581</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>592</v>
+        <v>535</v>
       </c>
       <c r="C5" t="n">
-        <v>1610</v>
+        <v>614</v>
       </c>
       <c r="D5" t="n">
-        <v>1280</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7293</v>
+        <v>7183</v>
       </c>
       <c r="C2" t="n">
-        <v>9557</v>
+        <v>6708</v>
       </c>
       <c r="D2" t="n">
-        <v>29292</v>
+        <v>28901</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4123</v>
+        <v>4288</v>
       </c>
       <c r="C3" t="n">
-        <v>6252</v>
+        <v>4647</v>
       </c>
       <c r="D3" t="n">
-        <v>11469</v>
+        <v>10003</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2563</v>
+        <v>2476</v>
       </c>
       <c r="C4" t="n">
-        <v>4557</v>
+        <v>3531</v>
       </c>
       <c r="D4" t="n">
-        <v>3656</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1158</v>
+        <v>1097</v>
       </c>
       <c r="C5" t="n">
-        <v>2503</v>
+        <v>1568</v>
       </c>
       <c r="D5" t="n">
-        <v>1453</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="C6" t="n">
+        <v>457</v>
+      </c>
+      <c r="D6" t="n">
         <v>953</v>
-      </c>
-      <c r="D6" t="n">
-        <v>959</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6530</v>
+        <v>8716</v>
       </c>
       <c r="C2" t="n">
-        <v>7967</v>
+        <v>12773</v>
       </c>
       <c r="D2" t="n">
-        <v>23863</v>
+        <v>32977</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4080</v>
+        <v>4191</v>
       </c>
       <c r="C3" t="n">
-        <v>6483</v>
+        <v>4669</v>
       </c>
       <c r="D3" t="n">
-        <v>12579</v>
+        <v>11450</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2045</v>
+        <v>2082</v>
       </c>
       <c r="C4" t="n">
-        <v>4479</v>
+        <v>3369</v>
       </c>
       <c r="D4" t="n">
-        <v>4337</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>968</v>
+        <v>930</v>
       </c>
       <c r="C5" t="n">
-        <v>2572</v>
+        <v>1907</v>
       </c>
       <c r="D5" t="n">
-        <v>1449</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C6" t="n">
-        <v>1157</v>
+        <v>682</v>
       </c>
       <c r="D6" t="n">
-        <v>782</v>
+        <v>777</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>259</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
         <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5436</v>
+        <v>6290</v>
       </c>
       <c r="C2" t="n">
-        <v>4482</v>
+        <v>9021</v>
       </c>
       <c r="D2" t="n">
-        <v>18992</v>
+        <v>33148</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4385</v>
+        <v>5373</v>
       </c>
       <c r="C3" t="n">
-        <v>6316</v>
+        <v>8096</v>
       </c>
       <c r="D3" t="n">
-        <v>13548</v>
+        <v>14223</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2678</v>
+        <v>2761</v>
       </c>
       <c r="C4" t="n">
-        <v>5578</v>
+        <v>4052</v>
       </c>
       <c r="D4" t="n">
-        <v>5866</v>
+        <v>5006</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="C5" t="n">
-        <v>3616</v>
+        <v>2737</v>
       </c>
       <c r="D5" t="n">
-        <v>1945</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="C6" t="n">
-        <v>1930</v>
+        <v>1379</v>
       </c>
       <c r="D6" t="n">
-        <v>898</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C7" t="n">
-        <v>814</v>
+        <v>499</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>321</v>
+        <v>243</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4327</v>
+        <v>4993</v>
       </c>
       <c r="C2" t="n">
-        <v>12355</v>
+        <v>6284</v>
       </c>
       <c r="D2" t="n">
-        <v>15341</v>
+        <v>28119</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4030</v>
+        <v>4800</v>
       </c>
       <c r="C3" t="n">
-        <v>4651</v>
+        <v>7444</v>
       </c>
       <c r="D3" t="n">
-        <v>13421</v>
+        <v>16226</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3025</v>
+        <v>3489</v>
       </c>
       <c r="C4" t="n">
-        <v>5812</v>
+        <v>6258</v>
       </c>
       <c r="D4" t="n">
-        <v>7032</v>
+        <v>6623</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1728</v>
+        <v>1771</v>
       </c>
       <c r="C5" t="n">
-        <v>4595</v>
+        <v>3399</v>
       </c>
       <c r="D5" t="n">
-        <v>2601</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C6" t="n">
-        <v>2782</v>
+        <v>2080</v>
       </c>
       <c r="D6" t="n">
-        <v>1057</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -6451,10 +6451,10 @@
         <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>1374</v>
+        <v>950</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>567</v>
+        <v>373</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6538,7 +6538,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_83_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_83_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5876</v>
+        <v>676</v>
       </c>
       <c r="C2" t="n">
-        <v>11840</v>
+        <v>4852</v>
       </c>
       <c r="D2" t="n">
-        <v>37670</v>
+        <v>20821</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4046</v>
+        <v>1220</v>
       </c>
       <c r="C3" t="n">
-        <v>6001</v>
+        <v>10617</v>
       </c>
       <c r="D3" t="n">
-        <v>16822</v>
+        <v>17177</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3504</v>
+        <v>884</v>
       </c>
       <c r="C4" t="n">
-        <v>6742</v>
+        <v>11072</v>
       </c>
       <c r="D4" t="n">
-        <v>8017</v>
+        <v>6764</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2257</v>
+        <v>475</v>
       </c>
       <c r="C5" t="n">
-        <v>4722</v>
+        <v>6626</v>
       </c>
       <c r="D5" t="n">
-        <v>2930</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1162</v>
+        <v>214</v>
       </c>
       <c r="C6" t="n">
-        <v>2703</v>
+        <v>2570</v>
       </c>
       <c r="D6" t="n">
-        <v>1179</v>
+        <v>727</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>522</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>1482</v>
+        <v>848</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>188</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>644</v>
+        <v>359</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7197</v>
+        <v>605</v>
       </c>
       <c r="C2" t="n">
-        <v>15976</v>
+        <v>10241</v>
       </c>
       <c r="D2" t="n">
-        <v>37809</v>
+        <v>17006</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3961</v>
+        <v>825</v>
       </c>
       <c r="C3" t="n">
-        <v>7579</v>
+        <v>6823</v>
       </c>
       <c r="D3" t="n">
-        <v>18526</v>
+        <v>16519</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3204</v>
+        <v>901</v>
       </c>
       <c r="C4" t="n">
-        <v>6188</v>
+        <v>10605</v>
       </c>
       <c r="D4" t="n">
-        <v>9210</v>
+        <v>8357</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2487</v>
+        <v>580</v>
       </c>
       <c r="C5" t="n">
-        <v>5554</v>
+        <v>8771</v>
       </c>
       <c r="D5" t="n">
-        <v>3594</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1468</v>
+        <v>297</v>
       </c>
       <c r="C6" t="n">
-        <v>3542</v>
+        <v>4476</v>
       </c>
       <c r="D6" t="n">
-        <v>1432</v>
+        <v>918</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>705</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>2019</v>
+        <v>1632</v>
       </c>
       <c r="D7" t="n">
-        <v>726</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>288</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>990</v>
+        <v>568</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>436</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10154</v>
+        <v>336</v>
       </c>
       <c r="C2" t="n">
-        <v>16723</v>
+        <v>4550</v>
       </c>
       <c r="D2" t="n">
-        <v>43899</v>
+        <v>11729</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4256</v>
+        <v>740</v>
       </c>
       <c r="C3" t="n">
-        <v>9698</v>
+        <v>7813</v>
       </c>
       <c r="D3" t="n">
-        <v>19654</v>
+        <v>16177</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2995</v>
+        <v>976</v>
       </c>
       <c r="C4" t="n">
-        <v>6587</v>
+        <v>10059</v>
       </c>
       <c r="D4" t="n">
-        <v>10183</v>
+        <v>9287</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2476</v>
+        <v>587</v>
       </c>
       <c r="C5" t="n">
-        <v>5646</v>
+        <v>10423</v>
       </c>
       <c r="D5" t="n">
-        <v>4293</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1713</v>
+        <v>242</v>
       </c>
       <c r="C6" t="n">
-        <v>4322</v>
+        <v>5408</v>
       </c>
       <c r="D6" t="n">
-        <v>1689</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>890</v>
+        <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>2595</v>
+        <v>1492</v>
       </c>
       <c r="D7" t="n">
-        <v>815</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>392</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1373</v>
+        <v>490</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>148</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>642</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>304</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9112</v>
+        <v>597</v>
       </c>
       <c r="C2" t="n">
-        <v>11639</v>
+        <v>12154</v>
       </c>
       <c r="D2" t="n">
-        <v>36062</v>
+        <v>11121</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5198</v>
+        <v>487</v>
       </c>
       <c r="C3" t="n">
-        <v>13831</v>
+        <v>5568</v>
       </c>
       <c r="D3" t="n">
-        <v>21052</v>
+        <v>14578</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2287</v>
+        <v>782</v>
       </c>
       <c r="C4" t="n">
-        <v>8961</v>
+        <v>8846</v>
       </c>
       <c r="D4" t="n">
-        <v>9614</v>
+        <v>10129</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1582</v>
+        <v>671</v>
       </c>
       <c r="C5" t="n">
-        <v>4235</v>
+        <v>10138</v>
       </c>
       <c r="D5" t="n">
-        <v>2809</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>822</v>
+        <v>339</v>
       </c>
       <c r="C6" t="n">
-        <v>2543</v>
+        <v>7576</v>
       </c>
       <c r="D6" t="n">
-        <v>798</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>362</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>1345</v>
+        <v>3132</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>629</v>
+        <v>872</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5421</v>
+        <v>407</v>
       </c>
       <c r="C2" t="n">
-        <v>5019</v>
+        <v>7782</v>
       </c>
       <c r="D2" t="n">
-        <v>24797</v>
+        <v>8355</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5810</v>
+        <v>458</v>
       </c>
       <c r="C3" t="n">
-        <v>11692</v>
+        <v>7466</v>
       </c>
       <c r="D3" t="n">
-        <v>22082</v>
+        <v>13370</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2942</v>
+        <v>634</v>
       </c>
       <c r="C4" t="n">
-        <v>11230</v>
+        <v>7532</v>
       </c>
       <c r="D4" t="n">
-        <v>11061</v>
+        <v>10516</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1754</v>
+        <v>693</v>
       </c>
       <c r="C5" t="n">
-        <v>6255</v>
+        <v>9832</v>
       </c>
       <c r="D5" t="n">
-        <v>3653</v>
+        <v>4584</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>975</v>
+        <v>404</v>
       </c>
       <c r="C6" t="n">
-        <v>3267</v>
+        <v>8705</v>
       </c>
       <c r="D6" t="n">
-        <v>985</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>337</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>1755</v>
+        <v>4477</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>838</v>
+        <v>1346</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>334</v>
+        <v>387</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6100</v>
+        <v>318</v>
       </c>
       <c r="C2" t="n">
-        <v>3633</v>
+        <v>13096</v>
       </c>
       <c r="D2" t="n">
-        <v>22784</v>
+        <v>16856</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4748</v>
+        <v>369</v>
       </c>
       <c r="C3" t="n">
-        <v>7732</v>
+        <v>6805</v>
       </c>
       <c r="D3" t="n">
-        <v>20967</v>
+        <v>11979</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3559</v>
+        <v>500</v>
       </c>
       <c r="C4" t="n">
-        <v>11213</v>
+        <v>7346</v>
       </c>
       <c r="D4" t="n">
-        <v>12523</v>
+        <v>10607</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1997</v>
+        <v>619</v>
       </c>
       <c r="C5" t="n">
-        <v>8369</v>
+        <v>8678</v>
       </c>
       <c r="D5" t="n">
-        <v>4679</v>
+        <v>5197</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1172</v>
+        <v>469</v>
       </c>
       <c r="C6" t="n">
-        <v>4527</v>
+        <v>9073</v>
       </c>
       <c r="D6" t="n">
-        <v>1356</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>503</v>
+        <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>2408</v>
+        <v>6135</v>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>167</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>1205</v>
+        <v>2450</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>519</v>
+        <v>710</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3705</v>
+        <v>226</v>
       </c>
       <c r="C2" t="n">
-        <v>1760</v>
+        <v>7438</v>
       </c>
       <c r="D2" t="n">
-        <v>15892</v>
+        <v>12406</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4877</v>
+        <v>499</v>
       </c>
       <c r="C3" t="n">
-        <v>6210</v>
+        <v>8852</v>
       </c>
       <c r="D3" t="n">
-        <v>20686</v>
+        <v>13291</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3923</v>
+        <v>823</v>
       </c>
       <c r="C4" t="n">
-        <v>10986</v>
+        <v>10436</v>
       </c>
       <c r="D4" t="n">
-        <v>13562</v>
+        <v>10717</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2067</v>
+        <v>450</v>
       </c>
       <c r="C5" t="n">
-        <v>10176</v>
+        <v>12778</v>
       </c>
       <c r="D5" t="n">
-        <v>4922</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>919</v>
+        <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>5249</v>
+        <v>7790</v>
       </c>
       <c r="D6" t="n">
-        <v>1310</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>154</v>
+        <v>56</v>
       </c>
       <c r="C7" t="n">
-        <v>2395</v>
+        <v>2401</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>851</v>
+        <v>695</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5122</v>
+        <v>131</v>
       </c>
       <c r="C2" t="n">
-        <v>8084</v>
+        <v>4279</v>
       </c>
       <c r="D2" t="n">
-        <v>16877</v>
+        <v>8546</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3773</v>
+        <v>334</v>
       </c>
       <c r="C3" t="n">
-        <v>3835</v>
+        <v>7301</v>
       </c>
       <c r="D3" t="n">
-        <v>18715</v>
+        <v>12263</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3743</v>
+        <v>568</v>
       </c>
       <c r="C4" t="n">
-        <v>8708</v>
+        <v>9085</v>
       </c>
       <c r="D4" t="n">
-        <v>14243</v>
+        <v>10331</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2473</v>
+        <v>420</v>
       </c>
       <c r="C5" t="n">
-        <v>10306</v>
+        <v>10404</v>
       </c>
       <c r="D5" t="n">
-        <v>6063</v>
+        <v>4832</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1209</v>
+        <v>157</v>
       </c>
       <c r="C6" t="n">
-        <v>7292</v>
+        <v>7936</v>
       </c>
       <c r="D6" t="n">
-        <v>1744</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>42</v>
       </c>
       <c r="C7" t="n">
-        <v>3480</v>
+        <v>3188</v>
       </c>
       <c r="D7" t="n">
-        <v>656</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1396</v>
+        <v>817</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>441</v>
+        <v>245</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3474</v>
+        <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>4276</v>
+        <v>7477</v>
       </c>
       <c r="D2" t="n">
-        <v>12700</v>
+        <v>8170</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3666</v>
+        <v>208</v>
       </c>
       <c r="C3" t="n">
-        <v>4925</v>
+        <v>5142</v>
       </c>
       <c r="D3" t="n">
-        <v>17520</v>
+        <v>10884</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3451</v>
+        <v>407</v>
       </c>
       <c r="C4" t="n">
-        <v>6906</v>
+        <v>7988</v>
       </c>
       <c r="D4" t="n">
-        <v>14504</v>
+        <v>10350</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2671</v>
+        <v>439</v>
       </c>
       <c r="C5" t="n">
-        <v>9950</v>
+        <v>9541</v>
       </c>
       <c r="D5" t="n">
-        <v>6858</v>
+        <v>5582</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1398</v>
+        <v>240</v>
       </c>
       <c r="C6" t="n">
-        <v>8443</v>
+        <v>9093</v>
       </c>
       <c r="D6" t="n">
-        <v>2089</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>4505</v>
+        <v>5327</v>
       </c>
       <c r="D7" t="n">
-        <v>740</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5029</v>
+        <v>246</v>
       </c>
       <c r="C2" t="n">
-        <v>8861</v>
+        <v>18953</v>
       </c>
       <c r="D2" t="n">
-        <v>19091</v>
+        <v>12283</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3037</v>
+        <v>173</v>
       </c>
       <c r="C3" t="n">
-        <v>4226</v>
+        <v>5438</v>
       </c>
       <c r="D3" t="n">
-        <v>15886</v>
+        <v>9822</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3059</v>
+        <v>285</v>
       </c>
       <c r="C4" t="n">
-        <v>5982</v>
+        <v>6510</v>
       </c>
       <c r="D4" t="n">
-        <v>14468</v>
+        <v>10018</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2663</v>
+        <v>391</v>
       </c>
       <c r="C5" t="n">
-        <v>8507</v>
+        <v>8656</v>
       </c>
       <c r="D5" t="n">
-        <v>7603</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1671</v>
+        <v>290</v>
       </c>
       <c r="C6" t="n">
-        <v>8925</v>
+        <v>9109</v>
       </c>
       <c r="D6" t="n">
-        <v>2591</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>541</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>5936</v>
+        <v>6911</v>
       </c>
       <c r="D7" t="n">
-        <v>891</v>
+        <v>875</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>2706</v>
+        <v>3244</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>897</v>
+        <v>1000</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6093</v>
+        <v>3220</v>
       </c>
       <c r="C2" t="n">
-        <v>3034</v>
+        <v>15717</v>
       </c>
       <c r="D2" t="n">
-        <v>11625</v>
+        <v>11868</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3715</v>
+        <v>151</v>
       </c>
       <c r="C2" t="n">
-        <v>5245</v>
+        <v>13923</v>
       </c>
       <c r="D2" t="n">
-        <v>14203</v>
+        <v>11527</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3951</v>
+        <v>164</v>
       </c>
       <c r="C3" t="n">
-        <v>5690</v>
+        <v>9396</v>
       </c>
       <c r="D3" t="n">
-        <v>17430</v>
+        <v>9484</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4024</v>
+        <v>211</v>
       </c>
       <c r="C4" t="n">
-        <v>8810</v>
+        <v>5879</v>
       </c>
       <c r="D4" t="n">
-        <v>14675</v>
+        <v>9590</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1544</v>
+        <v>324</v>
       </c>
       <c r="C5" t="n">
-        <v>12567</v>
+        <v>7631</v>
       </c>
       <c r="D5" t="n">
-        <v>6696</v>
+        <v>6477</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>499</v>
+        <v>304</v>
       </c>
       <c r="C6" t="n">
-        <v>7304</v>
+        <v>8775</v>
       </c>
       <c r="D6" t="n">
-        <v>2012</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>2651</v>
+        <v>7659</v>
       </c>
       <c r="D7" t="n">
-        <v>534</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>879</v>
+        <v>4572</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>1759</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>515</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>57</v>
+      </c>
+      <c r="D13" t="n">
         <v>37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6907</v>
+        <v>3484</v>
       </c>
       <c r="C2" t="n">
-        <v>6182</v>
+        <v>11041</v>
       </c>
       <c r="D2" t="n">
-        <v>12803</v>
+        <v>18652</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2589</v>
+        <v>1040</v>
       </c>
       <c r="C3" t="n">
-        <v>1529</v>
+        <v>6206</v>
       </c>
       <c r="D3" t="n">
-        <v>2592</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5069</v>
+        <v>1941</v>
       </c>
       <c r="C2" t="n">
-        <v>6731</v>
+        <v>11539</v>
       </c>
       <c r="D2" t="n">
-        <v>23124</v>
+        <v>30006</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3898</v>
+        <v>1912</v>
       </c>
       <c r="C3" t="n">
-        <v>3624</v>
+        <v>7886</v>
       </c>
       <c r="D3" t="n">
-        <v>4116</v>
+        <v>4956</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1158</v>
+        <v>507</v>
       </c>
       <c r="C4" t="n">
-        <v>953</v>
+        <v>3861</v>
       </c>
       <c r="D4" t="n">
-        <v>1703</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6985</v>
+        <v>1559</v>
       </c>
       <c r="C2" t="n">
-        <v>6033</v>
+        <v>5447</v>
       </c>
       <c r="D2" t="n">
-        <v>30715</v>
+        <v>26176</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3680</v>
+        <v>1590</v>
       </c>
       <c r="C3" t="n">
-        <v>4603</v>
+        <v>8583</v>
       </c>
       <c r="D3" t="n">
-        <v>6860</v>
+        <v>8799</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2140</v>
+        <v>1051</v>
       </c>
       <c r="C4" t="n">
-        <v>2446</v>
+        <v>6137</v>
       </c>
       <c r="D4" t="n">
-        <v>2114</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>535</v>
+        <v>259</v>
       </c>
       <c r="C5" t="n">
-        <v>614</v>
+        <v>2273</v>
       </c>
       <c r="D5" t="n">
-        <v>1232</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7183</v>
+        <v>1548</v>
       </c>
       <c r="C2" t="n">
-        <v>6708</v>
+        <v>12072</v>
       </c>
       <c r="D2" t="n">
-        <v>28901</v>
+        <v>30170</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4288</v>
+        <v>1303</v>
       </c>
       <c r="C3" t="n">
-        <v>4647</v>
+        <v>5988</v>
       </c>
       <c r="D3" t="n">
-        <v>10003</v>
+        <v>10945</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2476</v>
+        <v>1124</v>
       </c>
       <c r="C4" t="n">
-        <v>3531</v>
+        <v>7371</v>
       </c>
       <c r="D4" t="n">
-        <v>2895</v>
+        <v>3402</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1097</v>
+        <v>552</v>
       </c>
       <c r="C5" t="n">
-        <v>1568</v>
+        <v>4303</v>
       </c>
       <c r="D5" t="n">
-        <v>1355</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>294</v>
+        <v>166</v>
       </c>
       <c r="C6" t="n">
-        <v>457</v>
+        <v>1302</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>822</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>247</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8716</v>
+        <v>1178</v>
       </c>
       <c r="C2" t="n">
-        <v>12773</v>
+        <v>7668</v>
       </c>
       <c r="D2" t="n">
-        <v>32977</v>
+        <v>31581</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4191</v>
+        <v>1167</v>
       </c>
       <c r="C3" t="n">
-        <v>4669</v>
+        <v>7859</v>
       </c>
       <c r="D3" t="n">
-        <v>11450</v>
+        <v>12960</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2082</v>
+        <v>1035</v>
       </c>
       <c r="C4" t="n">
-        <v>3369</v>
+        <v>6500</v>
       </c>
       <c r="D4" t="n">
-        <v>3558</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>930</v>
+        <v>717</v>
       </c>
       <c r="C5" t="n">
-        <v>1907</v>
+        <v>5703</v>
       </c>
       <c r="D5" t="n">
-        <v>1293</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="C6" t="n">
-        <v>682</v>
+        <v>2757</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>877</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C7" t="n">
-        <v>259</v>
+        <v>777</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>299</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6290</v>
+        <v>1378</v>
       </c>
       <c r="C2" t="n">
-        <v>9021</v>
+        <v>18015</v>
       </c>
       <c r="D2" t="n">
-        <v>33148</v>
+        <v>38166</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5373</v>
+        <v>972</v>
       </c>
       <c r="C3" t="n">
-        <v>8096</v>
+        <v>6839</v>
       </c>
       <c r="D3" t="n">
-        <v>14223</v>
+        <v>14621</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2761</v>
+        <v>937</v>
       </c>
       <c r="C4" t="n">
-        <v>4052</v>
+        <v>6954</v>
       </c>
       <c r="D4" t="n">
-        <v>5006</v>
+        <v>5755</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1334</v>
+        <v>765</v>
       </c>
       <c r="C5" t="n">
-        <v>2737</v>
+        <v>5959</v>
       </c>
       <c r="D5" t="n">
-        <v>1710</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>589</v>
+        <v>432</v>
       </c>
       <c r="C6" t="n">
-        <v>1379</v>
+        <v>4059</v>
       </c>
       <c r="D6" t="n">
-        <v>857</v>
+        <v>977</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>499</v>
+        <v>1642</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>243</v>
+        <v>504</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4993</v>
+        <v>1276</v>
       </c>
       <c r="C2" t="n">
-        <v>6284</v>
+        <v>11529</v>
       </c>
       <c r="D2" t="n">
-        <v>28119</v>
+        <v>30343</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4800</v>
+        <v>1452</v>
       </c>
       <c r="C3" t="n">
-        <v>7444</v>
+        <v>11984</v>
       </c>
       <c r="D3" t="n">
-        <v>16226</v>
+        <v>15883</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3489</v>
+        <v>706</v>
       </c>
       <c r="C4" t="n">
-        <v>6258</v>
+        <v>9859</v>
       </c>
       <c r="D4" t="n">
-        <v>6623</v>
+        <v>5238</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1771</v>
+        <v>399</v>
       </c>
       <c r="C5" t="n">
-        <v>3399</v>
+        <v>3977</v>
       </c>
       <c r="D5" t="n">
-        <v>2242</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>871</v>
+        <v>164</v>
       </c>
       <c r="C6" t="n">
-        <v>2080</v>
+        <v>1609</v>
       </c>
       <c r="D6" t="n">
-        <v>1000</v>
+        <v>629</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>341</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>950</v>
+        <v>493</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>373</v>
+        <v>273</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
